--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -82,46 +82,61 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>JENKINS</t>
   </si>
   <si>
     <t>MIXCOHA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
     <t>EVARISTO</t>
   </si>
   <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
   </si>
   <si>
     <t>ANA KAREN</t>
   </si>
   <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>CRISTINA YAJANI</t>
+    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -691,16 +706,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>85.29000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -714,16 +732,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>70.27</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -760,16 +781,19 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>86.20999999999999</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -848,13 +872,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>91.18000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2">
         <v>8.699999999999999</v>
@@ -874,16 +898,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>86.48999999999999</v>
+        <v>70.27</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -926,16 +950,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>93.09999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -971,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1003,16 +1027,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920011</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1026,22 +1050,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920189</v>
+        <v>22330051920007</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1049,22 +1073,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920089</v>
+        <v>22330051920021</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1078,10 +1102,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1090,12 +1114,12 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920336</v>
+        <v>22330051920189</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1104,7 +1128,7 @@
         <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1113,6 +1137,52 @@
         <v>11</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920089</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920036</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -82,18 +82,24 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>JENKINS</t>
   </si>
   <si>
@@ -103,33 +109,51 @@
     <t>GIL</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
     <t>EVARISTO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
     <t>JOSE FRANCISCO</t>
   </si>
   <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
     <t>DIEGO IVAN</t>
   </si>
   <si>
+    <t>NAHUM HIRAM</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
@@ -137,6 +161,9 @@
   </si>
   <si>
     <t>JOSE RAUL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
   </si>
 </sst>
 </file>
@@ -758,16 +785,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>42.42</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -807,16 +837,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>72.73</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -924,16 +957,16 @@
         <v>0</v>
       </c>
       <c r="E4">
+        <v>19</v>
+      </c>
+      <c r="F4">
         <v>14</v>
       </c>
-      <c r="F4">
-        <v>19</v>
-      </c>
       <c r="G4">
-        <v>57.58</v>
+        <v>42.42</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -995,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1027,16 +1060,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920011</v>
+        <v>22330051920021</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1050,22 +1083,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920007</v>
+        <v>20330051920072</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1073,22 +1106,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920021</v>
+        <v>20330051920090</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1096,16 +1129,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920090</v>
+        <v>22330051920200</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1119,16 +1152,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920189</v>
+        <v>22330051920031</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1142,22 +1175,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920089</v>
+        <v>22330051920034</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1165,16 +1198,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920036</v>
+        <v>22330051920189</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1183,6 +1216,75 @@
         <v>11</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920089</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920036</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920367</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -103,9 +103,6 @@
     <t>JENKINS</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
     <t>GIL</t>
   </si>
   <si>
@@ -130,9 +127,6 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -155,9 +149,6 @@
   </si>
   <si>
     <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>JOSE RAUL</t>
@@ -1028,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1069,7 +1060,7 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,10 +1080,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1112,10 +1103,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1135,10 +1126,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1158,10 +1149,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1181,10 +1172,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1204,10 +1195,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1221,70 +1212,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920089</v>
+        <v>22330051920036</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920036</v>
+        <v>20330051920367</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920367</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
   </si>
   <si>
     <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
   </si>
   <si>
     <t>PAUL ARAVIER</t>
@@ -1019,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1051,22 +1045,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920021</v>
+        <v>20330051920072</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1074,7 +1068,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920072</v>
+        <v>20330051920090</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1083,7 +1077,7 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1097,7 +1091,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920090</v>
+        <v>22330051920200</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1106,7 +1100,7 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1120,7 +1114,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920200</v>
+        <v>22330051920031</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1129,13 +1123,13 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1143,7 +1137,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920031</v>
+        <v>22330051920034</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1152,7 +1146,7 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1166,7 +1160,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920034</v>
+        <v>22330051920189</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1175,7 +1169,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1189,7 +1183,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920189</v>
+        <v>22330051920036</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1198,7 +1192,7 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1207,52 +1201,29 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920036</v>
+        <v>20330051920367</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920367</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -82,28 +82,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>JENKINS</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
   </si>
   <si>
     <t>CASTAÑEDA</t>
@@ -112,19 +115,22 @@
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
   </si>
   <si>
     <t>PAUL ARAVIER</t>
@@ -133,22 +139,19 @@
     <t>DIEGO IVAN</t>
   </si>
   <si>
-    <t>NAHUM HIRAM</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
   </si>
 </sst>
 </file>
@@ -890,16 +893,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -916,16 +919,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>70.27</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -942,16 +945,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>42.42</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -968,16 +971,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>86.20999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -994,16 +997,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>72.73</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1045,7 +1048,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920072</v>
+        <v>22330051920382</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1054,13 +1057,13 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1068,7 +1071,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920090</v>
+        <v>20330051920072</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1077,7 +1080,7 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1091,7 +1094,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920200</v>
+        <v>20330051920090</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1100,7 +1103,7 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1114,7 +1117,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920031</v>
+        <v>22330051920034</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1123,7 +1126,7 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1137,7 +1140,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920034</v>
+        <v>22330051920189</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1146,7 +1149,7 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1160,7 +1163,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920189</v>
+        <v>21330051920203</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1169,13 +1172,13 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1183,7 +1186,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920036</v>
+        <v>21330051920213</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1192,36 +1195,36 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920367</v>
+        <v>22330051920018</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -94,9 +94,6 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
   </si>
   <si>
     <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
   </si>
   <si>
     <t>ANGEL DANIEL</t>
@@ -1016,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1054,10 +1045,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1077,10 +1068,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1100,10 +1091,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1123,10 +1114,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1140,22 +1131,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920189</v>
+        <v>21330051920203</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1163,16 +1154,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920203</v>
+        <v>21330051920213</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1186,47 +1177,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920213</v>
+        <v>22330051920018</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920018</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
@@ -91,7 +91,7 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>MIXCOHA</t>
   </si>
   <si>
     <t>PEREZ</t>
@@ -112,7 +112,7 @@
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>EVARISTO</t>
   </si>
   <si>
     <t>CONTRERAS</t>
@@ -133,7 +133,7 @@
     <t>DIEGO IVAN</t>
   </si>
   <si>
-    <t>CARLOS YAEL</t>
+    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>ANGEL DANIEL</t>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920034</v>
+        <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1120,10 +1120,10 @@
         <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>

--- a/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
+++ b/docentes/Garcia Felix Jose Antonio - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -100,12 +106,15 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>HERRERA</t>
+    <t>AVELINO</t>
   </si>
   <si>
     <t>ZARATE</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
@@ -121,12 +130,15 @@
     <t>ROSALES</t>
   </si>
   <si>
-    <t>AVELINO</t>
+    <t>KEVIN</t>
   </si>
   <si>
     <t>OSMAR UZIEL</t>
   </si>
   <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
@@ -140,9 +152,6 @@
   </si>
   <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,16 +1048,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920382</v>
+        <v>22330051920018</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1062,22 +1071,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920072</v>
+        <v>22330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1085,22 +1094,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920090</v>
+        <v>22330051920021</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1108,22 +1117,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920089</v>
+        <v>20330051920072</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1131,22 +1140,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920203</v>
+        <v>20330051920090</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1154,22 +1163,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920213</v>
+        <v>20330051920089</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1177,25 +1186,48 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920018</v>
+        <v>21330051920203</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920213</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
